--- a/PRAX.xlsx
+++ b/PRAX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ffda80931a57275/Desktop/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="156" documentId="8_{FBA4D71E-5122-4F8E-B95B-052D81D4F5E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF0456A7-AB84-482C-9145-F44829515BC6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC3B42A0-0E75-4FA5-856C-B9328F5F86EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="5640" windowWidth="19850" windowHeight="11930" activeTab="1" xr2:uid="{20CAC1B9-0FFE-44BE-B9CE-C76FF9530266}"/>
+    <workbookView xWindow="380" yWindow="380" windowWidth="19050" windowHeight="16100" xr2:uid="{20CAC1B9-0FFE-44BE-B9CE-C76FF9530266}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="73">
   <si>
     <t>Price</t>
   </si>
@@ -253,6 +253,12 @@
   </si>
   <si>
     <t>Day 84 CFB mADL11 -3.4 vs. -1.9 for placebo; p&lt;0.0049</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>9/27/26 PDUFA</t>
   </si>
 </sst>
 </file>
@@ -412,7 +418,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -422,6 +427,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -806,7 +814,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{174F2B26-F142-44B2-AD5E-74816F8A1D39}">
-  <dimension ref="B2:L15"/>
+  <dimension ref="B2:M15"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.08984375" style="1" customWidth="1"/>
@@ -814,117 +822,117 @@
     <col min="3" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="13" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="14" t="s">
+      <c r="D2" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="15"/>
+      <c r="E2" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="14"/>
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="L2" s="2">
-        <v>282.25</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
+      <c r="H3" s="7"/>
       <c r="K3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="3">
         <v>27.9</v>
       </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+      <c r="M3" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="8"/>
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H4" s="7"/>
       <c r="K4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="L4" s="3">
         <f>L2*L3</f>
-        <v>7874.7749999999996</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+        <v>8509.5</v>
+      </c>
+      <c r="M4" s="16"/>
+    </row>
+    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
+      <c r="E5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="7"/>
       <c r="K5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="L5" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="M5" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
+      <c r="H6" s="7"/>
       <c r="K6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="10"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="12"/>
+      <c r="M6" s="16" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B7" s="9"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="11"/>
       <c r="K7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="L7" s="3">
         <f>L4-L5+L6</f>
-        <v>6474.7749999999996</v>
-      </c>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+        <v>7109.5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
@@ -932,7 +940,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>24</v>
       </c>
@@ -940,7 +948,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>25</v>
       </c>
@@ -948,7 +956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>26</v>
       </c>
@@ -956,7 +964,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>27</v>
       </c>
@@ -964,7 +972,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
       <c r="K15" s="1" t="s">
         <v>57</v>
       </c>
@@ -1104,7 +1112,7 @@
       </c>
     </row>
     <row r="20" spans="2:10" ht="13" x14ac:dyDescent="0.3">
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="15" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1137,12 +1145,12 @@
       </c>
     </row>
     <row r="30" spans="2:10" ht="13" x14ac:dyDescent="0.3">
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="15" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="32" spans="2:10" ht="13" x14ac:dyDescent="0.3">
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="15" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1152,10 +1160,10 @@
       </c>
     </row>
     <row r="36" spans="3:16" ht="13" x14ac:dyDescent="0.3">
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="G36" s="15" t="s">
         <v>41</v>
       </c>
     </row>
